--- a/data/trans_dic/IQ2608_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IQ2608_R3-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59,7%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>77,34%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50,71%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>67,91%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>67,2%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>87,6%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>59,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,85; 77,15</t>
+          <t>47,58; 69,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,01; 76,28</t>
+          <t>67,29; 85,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,18; 93,7</t>
+          <t>90,75; 99,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,2; 85,76</t>
+          <t>31,44; 70,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,66; 70,76</t>
+          <t>55,51; 76,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,37; 85,92</t>
+          <t>56,95; 76,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,43; 99,02</t>
+          <t>79,44; 93,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,73; 71,84</t>
+          <t>41,88; 84,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,92; 70,81</t>
+          <t>55,78; 70,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,65; 79,29</t>
+          <t>65,48; 78,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87,25; 95,02</t>
+          <t>87,49; 95,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,72; 72,32</t>
+          <t>41,87; 69,95</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>57,24%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>71,45%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>52,01%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>54,71%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>78,15%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>88,55%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46,84%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>57,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>71,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>46,25; 62,17</t>
+          <t>49,11; 64,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,34; 84,36</t>
+          <t>62,9; 78,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,23; 93,65</t>
+          <t>77,38; 89,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,21; 68,7</t>
+          <t>34,06; 73,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,47; 64,37</t>
+          <t>47,59; 62,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,77; 78,61</t>
+          <t>70,91; 84,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,78; 89,23</t>
+          <t>82,05; 93,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,4; 76,25</t>
+          <t>22,68; 55,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,15; 61,45</t>
+          <t>50,45; 61,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,72; 79,71</t>
+          <t>69,2; 79,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81,48; 89,73</t>
+          <t>82,46; 89,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,43; 65,43</t>
+          <t>33,96; 61,18</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42,51%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90,84%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80,2%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>68,25%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>44,86%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>92,24%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>73,41%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72,29%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>42,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,2%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,86; 55,7</t>
+          <t>33,42; 51,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,26; 96,69</t>
+          <t>83,56; 95,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,16; 81,89</t>
+          <t>71,35; 87,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,04; 86,12</t>
+          <t>48,67; 84,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,42; 51,54</t>
+          <t>35,74; 55,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,38; 95,89</t>
+          <t>85,36; 96,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,29; 87,38</t>
+          <t>62,86; 81,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,41; 85,4</t>
+          <t>54,77; 85,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,08; 50,61</t>
+          <t>36,5; 50,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86,56; 94,79</t>
+          <t>86,89; 95,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,99; 83,16</t>
+          <t>70,23; 82,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,12; 82,15</t>
+          <t>57,4; 81,66</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56,1%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77,27%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>50,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>75,65%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>81,62%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>77,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,14; 60,0</t>
+          <t>47,19; 65,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,06; 83,27</t>
+          <t>68,49; 84,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,34; 87,71</t>
+          <t>81,62; 93,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,25; 69,37</t>
+          <t>68,43; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,85; 65,25</t>
+          <t>40,2; 59,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,7; 83,97</t>
+          <t>66,41; 83,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,94; 93,66</t>
+          <t>73,01; 88,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,34; 100,0</t>
+          <t>21,21; 69,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,52; 59,64</t>
+          <t>47,29; 60,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,23; 81,86</t>
+          <t>70,5; 81,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80,61; 89,65</t>
+          <t>80,09; 89,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,12; 80,31</t>
+          <t>43,54; 80,99</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>64,55%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>82,84%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>92,73%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>74,47%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>79,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,22; 76,42</t>
+          <t>51,54; 75,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,77; 91,05</t>
+          <t>69,37; 87,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,16; 97,27</t>
+          <t>84,42; 97,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52,9; 91,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,16; 76,55</t>
+          <t>50,92; 75,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,29; 88,03</t>
+          <t>70,64; 91,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,57; 97,61</t>
+          <t>84,89; 97,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,69; 89,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55,75; 72,32</t>
+          <t>55,19; 72,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73,17; 87,47</t>
+          <t>73,38; 87,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87,36; 96,38</t>
+          <t>87,2; 96,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,93; 96,0</t>
+          <t>75,17; 94,65</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92,73%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74,04%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>69,53%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>50,68%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>93,64%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>73,1%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,04%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,8; 61,89</t>
+          <t>57,2; 76,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,66; 97,76</t>
+          <t>85,35; 96,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62,36; 82,11</t>
+          <t>63,16; 82,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,0; 85,65</t>
+          <t>47,43; 85,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57,51; 76,44</t>
+          <t>40,44; 61,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84,98; 97,4</t>
+          <t>86,46; 97,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,88; 83,24</t>
+          <t>61,62; 81,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52,56; 86,04</t>
+          <t>36,88; 85,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,08; 66,09</t>
+          <t>52,88; 67,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88,38; 96,54</t>
+          <t>88,6; 96,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>66,72; 80,03</t>
+          <t>65,85; 79,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54,0; 82,06</t>
+          <t>51,8; 81,28</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>86,07%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>71,22%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72,88%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>53,26%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>83,27%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>68,79%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>60,62%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,22%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,0; 60,14</t>
+          <t>53,19; 67,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76,6; 88,35</t>
+          <t>80,32; 90,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62,59; 74,99</t>
+          <t>64,7; 76,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59,13; 86,85</t>
+          <t>60,06; 84,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,98; 67,05</t>
+          <t>45,87; 60,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,58; 90,53</t>
+          <t>77,16; 88,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,84; 77,04</t>
+          <t>62,59; 75,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,82; 85,55</t>
+          <t>53,85; 83,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,91; 62,32</t>
+          <t>52,14; 62,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80,98; 88,07</t>
+          <t>80,44; 88,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65,63; 74,83</t>
+          <t>65,84; 74,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,78; 82,96</t>
+          <t>60,55; 81,17</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>82,5%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>81,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>87,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>67,55%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>82,16%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>78,46%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>84,28%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>82,5%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>81,97%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,72%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>76,65; 86,87</t>
+          <t>77,32; 86,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,09; 83,3</t>
+          <t>76,7; 86,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79,73; 88,62</t>
+          <t>82,44; 91,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,9; 85,14</t>
+          <t>51,93; 80,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,47; 86,68</t>
+          <t>76,56; 86,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,34; 86,37</t>
+          <t>73,16; 83,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,81; 90,95</t>
+          <t>79,7; 88,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>53,37; 81,01</t>
+          <t>61,3; 87,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>78,78; 85,75</t>
+          <t>78,63; 85,23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76,42; 83,7</t>
+          <t>76,64; 83,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82,26; 88,47</t>
+          <t>82,41; 88,65</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>59,81; 79,91</t>
+          <t>59,75; 79,95</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>63,56%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>60,58%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>80,51%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>63,56%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57,54; 63,48</t>
+          <t>60,47; 66,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78,45; 83,3</t>
+          <t>79,41; 83,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78,02; 82,81</t>
+          <t>80,85; 85,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58,15; 71,23</t>
+          <t>61,81; 74,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60,82; 66,59</t>
+          <t>57,64; 63,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>79,33; 84,15</t>
+          <t>78,13; 83,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,0; 85,6</t>
+          <t>77,95; 82,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62,76; 75,49</t>
+          <t>56,85; 70,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60,12; 64,28</t>
+          <t>59,9; 64,22</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79,59; 83,12</t>
+          <t>79,62; 83,09</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80,28; 83,54</t>
+          <t>80,34; 83,56</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>62,92; 72,15</t>
+          <t>61,44; 70,9</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>80</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33050</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47992</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61885</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8908</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>33540</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>38258</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>49845</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9128</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33050</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47992</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61885</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>17026</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28079; 38104</t>
+          <t>26337; 38708</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31885; 43428</t>
+          <t>41756; 53271</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45622; 53320</t>
+          <t>58501; 63836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6084; 11545</t>
+          <t>5523; 12428</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26936; 39171</t>
+          <t>27413; 37947</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41806; 53316</t>
+          <t>32420; 43690</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58290; 63829</t>
+          <t>45205; 52964</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6533; 14793</t>
+          <t>5179; 10435</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57530; 74170</t>
+          <t>58426; 74251</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78110; 94341</t>
+          <t>77909; 93901</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105894; 115319</t>
+          <t>106183; 115739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14889; 24627</t>
+          <t>12532; 20938</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61510</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74804</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>91907</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15039</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>53202</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>78678</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>90495</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10756</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>61510</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74804</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91907</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>22886</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44977; 60454</t>
+          <t>52771; 69506</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71824; 84932</t>
+          <t>65856; 81996</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84042; 95710</t>
+          <t>84340; 97192</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6709; 15777</t>
+          <t>9848; 21115</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53162; 69173</t>
+          <t>46276; 60624</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66760; 82298</t>
+          <t>71388; 84756</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84785; 97258</t>
+          <t>83857; 95405</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11504; 24782</t>
+          <t>4590; 11256</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>102669; 125793</t>
+          <t>103277; 125633</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143179; 163712</t>
+          <t>142126; 162829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172097; 189517</t>
+          <t>174159; 189989</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20204; 36292</t>
+          <t>16695; 30075</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>29353</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62210</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54995</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9650</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>29657</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>60336</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>45964</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13906</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>29353</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62210</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54995</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25108</t>
+          <t>23647</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23042; 36821</t>
+          <t>23079; 35771</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56424; 63250</t>
+          <t>57221; 65603</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38919; 51271</t>
+          <t>48926; 60047</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10395; 16566</t>
+          <t>6882; 12003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23764; 35587</t>
+          <t>23628; 36435</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57785; 65662</t>
+          <t>55839; 63201</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48889; 59920</t>
+          <t>39353; 51103</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7616; 13719</t>
+          <t>10589; 16580</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50111; 68404</t>
+          <t>49326; 67606</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115896; 126918</t>
+          <t>116336; 127450</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91813; 109095</t>
+          <t>92128; 107933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20517; 29000</t>
+          <t>19215; 27334</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44045</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>63540</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>71880</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9897</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>36701</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>56414</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>61939</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6409</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44045</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63540</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71880</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16645</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30750; 43788</t>
+          <t>37048; 51036</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50011; 62102</t>
+          <t>56326; 69815</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55657; 66564</t>
+          <t>66261; 76088</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3115; 10168</t>
+          <t>7238; 10578</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37568; 51229</t>
+          <t>29339; 43553</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55670; 69048</t>
+          <t>49523; 62384</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65710; 76037</t>
+          <t>55410; 66866</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6866; 10839</t>
+          <t>3228; 10517</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70479; 90354</t>
+          <t>71648; 91019</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>110132; 128359</t>
+          <t>110553; 128186</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126617; 140816</t>
+          <t>125808; 141045</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11250; 20477</t>
+          <t>11233; 20894</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28280</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36753</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42544</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11044</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>26171</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>36367</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>39726</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7655</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>28280</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36753</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42544</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>19019</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21575; 30983</t>
+          <t>22768; 33246</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31508; 39974</t>
+          <t>31965; 40513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36053; 41672</t>
+          <t>38484; 44474</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5439; 9401</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23039; 33812</t>
+          <t>20643; 30719</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31464; 40560</t>
+          <t>31014; 40050</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39467; 44500</t>
+          <t>36368; 41657</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5729; 9546</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47231; 61267</t>
+          <t>46752; 61249</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65837; 78706</t>
+          <t>66025; 79061</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77250; 85224</t>
+          <t>77107; 85279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15883; 20081</t>
+          <t>16322; 20551</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>40066</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>52522</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42753</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11023</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>28409</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>49375</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>39200</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5683</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>40066</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>52522</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>42753</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>16688</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22313; 34692</t>
+          <t>33815; 45273</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45164; 51548</t>
+          <t>48344; 54753</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33442; 44032</t>
+          <t>36466; 47887</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3019; 7604</t>
+          <t>7519; 13476</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33995; 45188</t>
+          <t>22669; 34562</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48133; 55169</t>
+          <t>45588; 51554</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35731; 48062</t>
+          <t>33043; 43632</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9663; 15817</t>
+          <t>3281; 7622</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58827; 76110</t>
+          <t>60903; 77176</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96659; 105587</t>
+          <t>96905; 105605</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74299; 89129</t>
+          <t>73335; 89040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14722; 22372</t>
+          <t>12823; 20118</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>143</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>80357</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>118677</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>101726</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>29732</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>68154</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>111827</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>94090</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>21048</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>80357</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>118677</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>101726</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>32665</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>53713</t>
+          <t>48983</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>58855; 76954</t>
+          <t>70510; 89794</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>102867; 118645</t>
+          <t>110753; 124798</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85606; 102567</t>
+          <t>92414; 109746</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16698; 24526</t>
+          <t>24503; 34601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>70234; 88884</t>
+          <t>58700; 77589</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>111114; 124830</t>
+          <t>103620; 118810</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92619; 110039</t>
+          <t>85607; 103369</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>26558; 37357</t>
+          <t>14536; 22471</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>135247; 162364</t>
+          <t>135834; 161819</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>220408; 239705</t>
+          <t>218952; 239859</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>183503; 209233</t>
+          <t>184107; 208918</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45145; 59658</t>
+          <t>41047; 55026</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>218</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>132851</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>137722</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>146106</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>26663</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>126839</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>126477</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>137109</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>18632</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>132851</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>137722</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>146106</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>26831</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>46169</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>118333; 134120</t>
+          <t>124521; 139802</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>117829; 134288</t>
+          <t>128870; 145368</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>129715; 144180</t>
+          <t>138452; 152850</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14438; 21604</t>
+          <t>20497; 31900</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>124762; 139592</t>
+          <t>118195; 133549</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>129955; 145114</t>
+          <t>117939; 134152</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>139085; 152743</t>
+          <t>129661; 143379</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20862; 31664</t>
+          <t>15825; 22547</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>248495; 270469</t>
+          <t>248016; 268826</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>251578; 275552</t>
+          <t>252325; 275231</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>271981; 292521</t>
+          <t>272469; 293096</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>38555; 51509</t>
+          <t>39007; 52194</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>801</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>845</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>146</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>449512</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>594219</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>613797</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>121957</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>402674</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>557731</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>558368</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>93216</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>449512</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>594219</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>613797</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>211062</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>382463; 421897</t>
+          <t>427713; 469268</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>541099; 574532</t>
+          <t>576562; 609777</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>541123; 574331</t>
+          <t>596134; 629014</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>83202; 101927</t>
+          <t>110250; 133410</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>430161; 470967</t>
+          <t>383130; 422022</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>575995; 611031</t>
+          <t>538893; 573373</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>597211; 631168</t>
+          <t>540588; 573493</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>120350; 144765</t>
+          <t>79324; 97910</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>824752; 881865</t>
+          <t>821846; 881029</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1126863; 1176791</t>
+          <t>1127254; 1176340</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1148659; 1195316</t>
+          <t>1149605; 1195652</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>210701; 241588</t>
+          <t>195323; 225383</t>
         </is>
       </c>
     </row>
